--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ramsis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ramsis\Ramsis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4D0EA81-F04F-4A79-BFF0-D0A859B3732C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F66106EE-7345-4B7B-8E25-2E718A4AEE93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4DDEB72C-A980-4D79-857B-3537438EF56D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="48">
   <si>
     <t>Item</t>
   </si>
@@ -174,6 +174,15 @@
   </si>
   <si>
     <t>https://makerselectronics.com/product/speaker-4-ohm-3w-55mm/</t>
+  </si>
+  <si>
+    <t>https://www.ram-e-shop.com/ar/shop/3mm-led-gg-led-3mm-green-color-lyd-3mm-lwn-khdr-6194</t>
+  </si>
+  <si>
+    <t>Led Green</t>
+  </si>
+  <si>
+    <t>run when switch is open</t>
   </si>
 </sst>
 </file>
@@ -565,7 +574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B054537-A1C5-45E7-9DD1-28CB552447C5}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -771,71 +780,88 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13">
-        <v>0.3</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" t="s">
-        <v>35</v>
+        <v>32</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14">
-        <v>45</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
         <v>35</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15">
-        <v>17.489999999999998</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C16" t="s">
         <v>35</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16">
+        <v>2</v>
+      </c>
+      <c r="E16">
+        <v>17.489999999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" t="s">
         <v>35</v>
       </c>
-      <c r="E16">
-        <f>SUM(E2:E15)</f>
-        <v>94.929999999999993</v>
+      <c r="C17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E17">
+        <f>SUM(E2:E16)</f>
+        <v>94.939999999999984</v>
       </c>
     </row>
   </sheetData>
@@ -844,10 +870,11 @@
     <hyperlink ref="C3" r:id="rId2" xr:uid="{1A0D7F6B-9744-469E-AC76-35D9B522277F}"/>
     <hyperlink ref="C4" r:id="rId3" xr:uid="{0AD7EA5C-EA6A-4B19-BD7A-92083AF34BE0}"/>
     <hyperlink ref="C9" r:id="rId4" xr:uid="{202B9FA1-2AF9-4866-9087-972E86BA31A6}"/>
-    <hyperlink ref="C13" r:id="rId5" xr:uid="{641BD50D-1AF0-4E48-A277-B58478DA8D00}"/>
+    <hyperlink ref="C14" r:id="rId5" xr:uid="{641BD50D-1AF0-4E48-A277-B58478DA8D00}"/>
     <hyperlink ref="C11" r:id="rId6" xr:uid="{3123405C-A8FC-4A09-BAB0-7C3D3538FF88}"/>
     <hyperlink ref="C12" r:id="rId7" xr:uid="{49A8B9EA-D021-4D8F-ABFF-4E9C78BCB625}"/>
     <hyperlink ref="C6" r:id="rId8" xr:uid="{61B1A251-566D-494A-A1C5-8162BD83641E}"/>
+    <hyperlink ref="C13" r:id="rId9" xr:uid="{A285C140-19F7-4DBE-B928-0E1348B9BA89}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
